--- a/data/trans_dic/IP19C02-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP19C02-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que en su última visita al dentista fue por limpieza de boca</t>
+          <t>Menores que en su última visita al dentista fue por limpieza de boca (tasa de respuesta: 99,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,18; 32,52</t>
+          <t>6,26; 33,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,33</t>
+          <t>0,0; 18,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,16; 17,36</t>
+          <t>1,91; 18,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,81; 41,41</t>
+          <t>5,56; 38,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,55; 21,26</t>
+          <t>2,55; 22,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,99; 16,02</t>
+          <t>1,97; 17,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,86</t>
+          <t>0,0; 10,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,34; 27,61</t>
+          <t>4,41; 27,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,91; 20,3</t>
+          <t>5,5; 21,25</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,27; 12,42</t>
+          <t>1,27; 12,02</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,83; 10,3</t>
+          <t>1,87; 10,47</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,43; 28,18</t>
+          <t>7,5; 28,54</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 10,59</t>
+          <t>1,17; 10,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,57</t>
+          <t>0,0; 7,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,31; 14,87</t>
+          <t>2,34; 14,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,31; 13,38</t>
+          <t>2,99; 13,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,05; 10,11</t>
+          <t>1,03; 10,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,97; 18,58</t>
+          <t>4,58; 17,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,34; 18,17</t>
+          <t>3,63; 16,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 6,72</t>
+          <t>1,25; 7,31</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,4; 7,86</t>
+          <t>1,67; 7,41</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,19; 11,18</t>
+          <t>3,24; 11,18</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,6; 12,85</t>
+          <t>4,22; 13,29</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,0; 17,37</t>
+          <t>1,99; 17,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,78</t>
+          <t>0,0; 10,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,38; 23,56</t>
+          <t>2,5; 21,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,88; 16,04</t>
+          <t>1,87; 16,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,97</t>
+          <t>0,0; 8,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 14,27</t>
+          <t>1,73; 14,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,28</t>
+          <t>0,0; 11,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,64; 17,39</t>
+          <t>1,59; 16,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,11; 10,07</t>
+          <t>1,14; 11,27</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 9,45</t>
+          <t>0,97; 8,77</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,22; 12,91</t>
+          <t>2,28; 13,83</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,59; 13,15</t>
+          <t>2,62; 12,86</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,36</t>
+          <t>0,0; 11,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,65</t>
+          <t>0,0; 9,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,78; 22,37</t>
+          <t>6,13; 22,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,42; 22,91</t>
+          <t>4,53; 22,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 3,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,14; 22,26</t>
+          <t>3,17; 20,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 14,31</t>
+          <t>1,59; 14,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,04; 23,64</t>
+          <t>1,73; 25,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,88</t>
+          <t>0,0; 7,03</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,55; 11,96</t>
+          <t>2,35; 12,93</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,12; 15,66</t>
+          <t>4,86; 15,44</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,68; 18,54</t>
+          <t>4,98; 19,59</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,33; 40,11</t>
+          <t>12,58; 39,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,59</t>
+          <t>0,0; 19,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50,02; 88,2</t>
+          <t>51,68; 89,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57,84; 82,18</t>
+          <t>59,34; 83,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,2; 28,59</t>
+          <t>3,15; 28,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,34</t>
+          <t>0,0; 14,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,46; 89,15</t>
+          <t>55,58; 88,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>62,2; 84,51</t>
+          <t>61,07; 84,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,16; 28,71</t>
+          <t>10,09; 28,81</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,36; 12,8</t>
+          <t>1,4; 14,02</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58,41; 85,17</t>
+          <t>59,53; 84,89</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>63,61; 80,87</t>
+          <t>63,65; 80,87</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,54</t>
+          <t>0,0; 16,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,06; 15,46</t>
+          <t>2,04; 17,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16,33; 39,09</t>
+          <t>14,96; 39,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,53</t>
+          <t>0,0; 13,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,28</t>
+          <t>0,0; 14,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,09; 19,8</t>
+          <t>2,08; 20,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,84; 31,85</t>
+          <t>9,86; 33,47</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,36; 12,64</t>
+          <t>1,17; 11,21</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,19; 14,27</t>
+          <t>3,22; 15,02</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15,51; 31,78</t>
+          <t>15,89; 31,59</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,12</t>
+          <t>0,0; 6,83</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,21; 14,28</t>
+          <t>3,27; 13,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,13; 10,35</t>
+          <t>1,15; 11,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,22; 21,8</t>
+          <t>8,36; 22,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,58; 23,81</t>
+          <t>9,53; 24,36</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,15; 13,49</t>
+          <t>3,08; 14,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,96; 9,48</t>
+          <t>0,97; 9,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,75; 34,77</t>
+          <t>16,61; 35,08</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12,89; 33,7</t>
+          <t>13,82; 32,79</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,14; 11,66</t>
+          <t>4,18; 12,04</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,05; 8,19</t>
+          <t>2,05; 7,82</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14,02; 25,86</t>
+          <t>13,77; 25,66</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,41; 25,43</t>
+          <t>13,81; 26,09</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,22; 13,67</t>
+          <t>4,23; 13,48</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,64; 18,38</t>
+          <t>6,38; 18,24</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24,76; 41,32</t>
+          <t>24,16; 40,3</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>73,06; 87,71</t>
+          <t>73,48; 87,96</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,47; 18,05</t>
+          <t>6,04; 17,54</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,35; 15,86</t>
+          <t>4,65; 16,21</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,9; 41,9</t>
+          <t>24,43; 42,64</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>74,79; 89,06</t>
+          <t>75,29; 88,53</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,21; 13,46</t>
+          <t>6,39; 13,52</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6,8; 14,93</t>
+          <t>6,68; 14,63</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26,53; 38,5</t>
+          <t>26,65; 38,65</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>75,9; 86,28</t>
+          <t>77,02; 87,1</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,47; 9,96</t>
+          <t>5,2; 9,63</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,02; 8,09</t>
+          <t>3,9; 8,19</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15,77; 22,53</t>
+          <t>15,74; 22,65</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>25,58; 33,85</t>
+          <t>25,63; 34,09</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,79; 9,18</t>
+          <t>4,89; 9,04</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,56; 8,85</t>
+          <t>4,61; 8,85</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,92; 23,03</t>
+          <t>16,14; 23,27</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>27,22; 35,7</t>
+          <t>27,38; 35,86</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,61; 8,89</t>
+          <t>5,53; 8,65</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4,69; 7,74</t>
+          <t>4,76; 7,81</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16,83; 21,65</t>
+          <t>16,97; 21,77</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>27,74; 33,94</t>
+          <t>27,7; 33,7</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en su última visita al dentista fue por limpieza de boca (tasa de respuesta: 99,44%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>3084</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2200</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5867</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2185</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1906</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>5083</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>5269</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2724</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2835</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>10950</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1209; 6465</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4100</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>545; 5236</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1935; 13511</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>676; 5931</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>585; 5143</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3262</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1758; 10836</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2523; 9741</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>663; 6253</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>1091; 6122</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>5600; 21314</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1314</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4353</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>4152</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2184</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>5683</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>6827</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>4152</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>4183</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>6997</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>11180</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>622; 5339</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4007</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1614; 10048</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1941; 8591</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>596; 5826</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>2600; 9799</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>2680; 12373</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1524; 8936</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>1849; 8206</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3576; 12327</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>6028; 18968</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2172</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3130</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1864</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2127</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>718</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2517</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>2808</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2782</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3848</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>4381</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>684; 5889</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3631</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>814; 7054</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>594; 5092</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3149</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>682; 5618</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3633</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>638; 6449</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>794; 7849</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>705; 6394</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>1473; 8938</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>1882; 9245</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1664</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1068</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5826</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5097</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>3859</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3152</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>5386</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1664</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>4927</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>8978</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>10483</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4935</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3768</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2851; 10676</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>1941; 9474</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1307; 8335</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>813; 7202</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1015; 14866</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5881</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>1953; 10739</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>4739; 15064</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>5057; 19886</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>6112</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1662</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>10778</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>18153</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2804</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>12695</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>25641</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>8916</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>2962</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>23472</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>43793</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>3296; 10346</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5049</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>7775; 13444</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>15007; 21136</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>708; 6346</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4016</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>9486; 15168</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>21146; 29191</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>4909; 14019</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>752; 7530</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>19117; 27259</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>38139; 48457</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>1372</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2207</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>10360</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1091</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1187</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>2849</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>8122</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>2559</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>5056</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>18482</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>1091</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4198</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>709; 5904</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>5945; 15712</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3772</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4204</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>691; 6697</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>4000; 13579</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>628; 6017</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>2182; 10190</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>12762; 25369</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3680</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>4906</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>3057</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>9417</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>12233</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>4918</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>2588</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>15410</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>22850</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>9824</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>5645</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>24827</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>35083</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>2134; 9046</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>738; 7319</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>5637; 14888</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>7412; 18943</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2096; 9864</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>653; 6066</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>10289; 21730</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>15018; 35639</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>5571; 16052</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>2692; 10255</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>17822; 33195</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>25755; 48642</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>6431</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>8893</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>25753</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>67682</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>8260</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>6400</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>25524</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>84206</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>14691</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>15293</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>51276</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>151888</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>3441; 10959</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>4964; 14198</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>19147; 31939</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>61208; 73269</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>4496; 13052</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>3258; 11364</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>19216; 33540</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>76629; 90100</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>9959; 21060</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>9877; 21643</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>42086; 61030</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>142539; 161194</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>25741</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>20361</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>68778</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>116339</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>24141</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>23211</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>71938</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>152510</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>49882</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>43572</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>140716</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>268849</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>18261; 33783</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>13779; 28946</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>57080; 82128</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>100387; 133507</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>17678; 32695</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>16876; 32379</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>59392; 85650</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>132619; 173719</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>39392; 61615</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>34252; 56189</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>123958; 159082</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>242682; 295243</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP19C02-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP19C02-Provincia-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,26; 33,46</t>
+          <t>5,9; 31,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,32</t>
+          <t>0,0; 19,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,91; 18,33</t>
+          <t>2,01; 17,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,56; 38,8</t>
+          <t>6,06; 38,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,55; 22,36</t>
+          <t>2,56; 21,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,97; 17,34</t>
+          <t>2,04; 17,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,91</t>
+          <t>0,0; 10,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,41; 27,18</t>
+          <t>4,73; 25,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,5; 21,25</t>
+          <t>5,44; 21,27</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,27; 12,02</t>
+          <t>2,29; 12,95</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,87; 10,47</t>
+          <t>1,83; 10,59</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,5; 28,54</t>
+          <t>7,26; 26,21</t>
         </is>
       </c>
     </row>
@@ -862,57 +862,57 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,17; 10,07</t>
+          <t>0,0; 9,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,49</t>
+          <t>0,0; 7,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,34; 14,6</t>
+          <t>2,3; 14,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,99; 13,22</t>
+          <t>3,03; 13,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,03; 10,11</t>
+          <t>1,04; 10,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,58; 17,27</t>
+          <t>5,01; 17,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,63; 16,76</t>
+          <t>4,31; 17,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 7,31</t>
+          <t>1,24; 7,1</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,67; 7,41</t>
+          <t>1,71; 8,23</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,24; 11,18</t>
+          <t>3,18; 10,83</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,22; 13,29</t>
+          <t>4,11; 12,99</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,99; 17,17</t>
+          <t>2,01; 16,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,85</t>
+          <t>0,0; 9,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,5; 21,69</t>
+          <t>2,54; 21,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,87; 16,0</t>
+          <t>1,84; 16,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,91</t>
+          <t>0,0; 9,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,73; 14,24</t>
+          <t>1,73; 14,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,31</t>
+          <t>0,0; 11,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,59; 16,1</t>
+          <t>1,61; 17,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 11,27</t>
+          <t>1,0; 9,27</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 8,77</t>
+          <t>1,01; 9,49</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,28; 13,83</t>
+          <t>2,33; 12,93</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,62; 12,86</t>
+          <t>2,65; 13,1</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,76</t>
+          <t>0,0; 12,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,02</t>
+          <t>0,0; 8,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,13; 22,94</t>
+          <t>6,03; 23,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,53; 22,11</t>
+          <t>4,65; 23,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1162,37 +1162,37 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,17; 20,22</t>
+          <t>3,13; 21,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,59; 14,12</t>
+          <t>1,62; 13,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 25,34</t>
+          <t>2,46; 27,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,03</t>
+          <t>0,0; 6,77</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,35; 12,93</t>
+          <t>2,37; 12,39</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,86; 15,44</t>
+          <t>4,61; 15,03</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,98; 19,59</t>
+          <t>4,75; 19,54</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,58; 39,5</t>
+          <t>10,83; 36,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,37</t>
+          <t>0,0; 19,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51,68; 89,36</t>
+          <t>47,24; 87,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59,34; 83,57</t>
+          <t>57,85; 82,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,15; 28,25</t>
+          <t>3,23; 28,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,54</t>
+          <t>0,0; 16,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,58; 88,87</t>
+          <t>54,17; 89,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>61,07; 84,3</t>
+          <t>61,7; 84,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,09; 28,81</t>
+          <t>9,83; 27,96</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,4; 14,02</t>
+          <t>1,41; 12,82</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59,53; 84,89</t>
+          <t>56,56; 83,12</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>63,65; 80,87</t>
+          <t>63,19; 80,69</t>
         </is>
       </c>
     </row>
@@ -1417,37 +1417,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,57</t>
+          <t>0,0; 18,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,04; 17,02</t>
+          <t>2,01; 15,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14,96; 39,54</t>
+          <t>16,61; 39,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,99</t>
+          <t>0,0; 12,7</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,82</t>
+          <t>0,0; 14,23</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,08; 20,2</t>
+          <t>2,11; 19,34</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,86; 33,47</t>
+          <t>9,78; 32,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1457,22 +1457,22 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,17; 11,21</t>
+          <t>1,18; 10,98</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,22; 15,02</t>
+          <t>3,22; 14,21</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15,89; 31,59</t>
+          <t>15,22; 31,65</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,83</t>
+          <t>0,0; 6,25</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,27; 13,86</t>
+          <t>3,22; 14,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,15; 11,44</t>
+          <t>1,15; 12,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,36; 22,08</t>
+          <t>7,98; 22,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,53; 24,36</t>
+          <t>9,24; 23,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,08; 14,5</t>
+          <t>3,13; 13,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,97; 9,03</t>
+          <t>0,95; 9,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,61; 35,08</t>
+          <t>15,89; 34,95</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,82; 32,79</t>
+          <t>13,25; 32,43</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,18; 12,04</t>
+          <t>4,16; 11,92</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,05; 7,82</t>
+          <t>1,95; 7,87</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13,77; 25,66</t>
+          <t>14,21; 25,51</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,81; 26,09</t>
+          <t>13,35; 25,8</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,23; 13,48</t>
+          <t>4,04; 13,07</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,38; 18,24</t>
+          <t>6,49; 18,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24,16; 40,3</t>
+          <t>24,63; 41,34</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>73,48; 87,96</t>
+          <t>73,1; 87,36</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,04; 17,54</t>
+          <t>6,31; 18,36</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,65; 16,21</t>
+          <t>4,33; 16,22</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,43; 42,64</t>
+          <t>23,77; 41,98</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>75,29; 88,53</t>
+          <t>75,32; 88,63</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,39; 13,52</t>
+          <t>6,17; 13,84</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6,68; 14,63</t>
+          <t>6,59; 14,91</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26,65; 38,65</t>
+          <t>26,9; 38,95</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>77,02; 87,1</t>
+          <t>76,33; 86,97</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,2; 9,63</t>
+          <t>5,27; 9,88</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,9; 8,19</t>
+          <t>3,92; 7,92</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15,74; 22,65</t>
+          <t>15,68; 22,44</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>25,63; 34,09</t>
+          <t>25,56; 33,51</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,89; 9,04</t>
+          <t>4,79; 9,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,61; 8,85</t>
+          <t>4,56; 8,66</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,14; 23,27</t>
+          <t>16,33; 23,38</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>27,38; 35,86</t>
+          <t>27,2; 35,82</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,53; 8,65</t>
+          <t>5,59; 8,53</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4,76; 7,81</t>
+          <t>4,8; 7,49</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16,97; 21,77</t>
+          <t>17,07; 21,7</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>27,7; 33,7</t>
+          <t>27,75; 33,78</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1209; 6465</t>
+          <t>1140; 6119</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4100</t>
+          <t>0; 4421</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>545; 5236</t>
+          <t>574; 4932</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1935; 13511</t>
+          <t>2110; 13269</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>676; 5931</t>
+          <t>678; 5610</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>585; 5143</t>
+          <t>606; 5182</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3262</t>
+          <t>0; 3249</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1758; 10836</t>
+          <t>1886; 10300</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2523; 9741</t>
+          <t>2494; 9749</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>663; 6253</t>
+          <t>1190; 6736</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1091; 6122</t>
+          <t>1072; 6195</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5600; 21314</t>
+          <t>5418; 19572</t>
         </is>
       </c>
     </row>
@@ -2422,57 +2422,57 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>622; 5339</t>
+          <t>0; 4832</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4007</t>
+          <t>0; 4089</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1614; 10048</t>
+          <t>1582; 10128</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1941; 8591</t>
+          <t>1967; 8463</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>596; 5826</t>
+          <t>598; 5941</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2600; 9799</t>
+          <t>2842; 10099</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2680; 12373</t>
+          <t>3185; 13092</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1524; 8936</t>
+          <t>1517; 8676</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1849; 8206</t>
+          <t>1894; 9108</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3576; 12327</t>
+          <t>3504; 11944</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6028; 18968</t>
+          <t>5867; 18530</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>684; 5889</t>
+          <t>690; 5715</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3631</t>
+          <t>0; 3326</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>814; 7054</t>
+          <t>825; 7045</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>594; 5092</t>
+          <t>587; 5098</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3149</t>
+          <t>0; 3406</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>682; 5618</t>
+          <t>681; 5728</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3633</t>
+          <t>0; 3671</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>638; 6449</t>
+          <t>645; 7125</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>794; 7849</t>
+          <t>693; 6451</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>705; 6394</t>
+          <t>735; 6918</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1473; 8938</t>
+          <t>1505; 8361</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1882; 9245</t>
+          <t>1908; 9416</t>
         </is>
       </c>
     </row>
@@ -2833,22 +2833,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4935</t>
+          <t>0; 5417</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3768</t>
+          <t>0; 3520</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2851; 10676</t>
+          <t>2806; 10718</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1941; 9474</t>
+          <t>1993; 9954</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2858,37 +2858,37 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1307; 8335</t>
+          <t>1290; 8775</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>813; 7202</t>
+          <t>827; 7040</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1015; 14866</t>
+          <t>1441; 15843</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 5881</t>
+          <t>0; 5658</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1953; 10739</t>
+          <t>1965; 10284</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4739; 15064</t>
+          <t>4498; 14658</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5057; 19886</t>
+          <t>4823; 19833</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3296; 10346</t>
+          <t>2836; 9656</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 5049</t>
+          <t>0; 5097</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7775; 13444</t>
+          <t>7107; 13210</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15007; 21136</t>
+          <t>14632; 20910</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>708; 6346</t>
+          <t>727; 6389</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 4016</t>
+          <t>0; 4576</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9486; 15168</t>
+          <t>9246; 15200</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>21146; 29191</t>
+          <t>21363; 29328</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4909; 14019</t>
+          <t>4782; 13607</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>752; 7530</t>
+          <t>760; 6885</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19117; 27259</t>
+          <t>18162; 26691</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>38139; 48457</t>
+          <t>37862; 48350</t>
         </is>
       </c>
     </row>
@@ -3249,37 +3249,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4198</t>
+          <t>0; 4606</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>709; 5904</t>
+          <t>696; 5441</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5945; 15712</t>
+          <t>6603; 15671</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 3772</t>
+          <t>0; 3424</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4204</t>
+          <t>0; 4034</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>691; 6697</t>
+          <t>699; 6414</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4000; 13579</t>
+          <t>3968; 12986</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -3289,22 +3289,22 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>628; 6017</t>
+          <t>632; 5896</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2182; 10190</t>
+          <t>2184; 9642</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12762; 25369</t>
+          <t>12227; 25417</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 3680</t>
+          <t>0; 3369</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2134; 9046</t>
+          <t>2101; 9778</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>738; 7319</t>
+          <t>733; 8257</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5637; 14888</t>
+          <t>5383; 14919</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7412; 18943</t>
+          <t>7186; 18370</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2096; 9864</t>
+          <t>2127; 9238</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>653; 6066</t>
+          <t>638; 6384</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10289; 21730</t>
+          <t>9840; 21652</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>15018; 35639</t>
+          <t>14396; 35250</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5571; 16052</t>
+          <t>5545; 15888</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2692; 10255</t>
+          <t>2561; 10314</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17822; 33195</t>
+          <t>18380; 33008</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>25755; 48642</t>
+          <t>24892; 48098</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>3441; 10959</t>
+          <t>3286; 10630</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>4964; 14198</t>
+          <t>5053; 14167</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>19147; 31939</t>
+          <t>19518; 32760</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>61208; 73269</t>
+          <t>60887; 72768</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4496; 13052</t>
+          <t>4696; 13665</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3258; 11364</t>
+          <t>3032; 11369</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>19216; 33540</t>
+          <t>18696; 33018</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>76629; 90100</t>
+          <t>76656; 90207</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>9959; 21060</t>
+          <t>9611; 21551</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>9877; 21643</t>
+          <t>9748; 22052</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>42086; 61030</t>
+          <t>42474; 61511</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>142539; 161194</t>
+          <t>141267; 160955</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>18261; 33783</t>
+          <t>18506; 34662</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>13779; 28946</t>
+          <t>13830; 27968</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>57080; 82128</t>
+          <t>56846; 81368</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>100387; 133507</t>
+          <t>100101; 131230</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>17678; 32695</t>
+          <t>17312; 32665</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16876; 32379</t>
+          <t>16690; 31697</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>59392; 85650</t>
+          <t>60081; 86057</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>132619; 173719</t>
+          <t>131763; 173549</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>39392; 61615</t>
+          <t>39819; 60805</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>34252; 56189</t>
+          <t>34508; 53864</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>123958; 159082</t>
+          <t>124700; 158533</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>242682; 295243</t>
+          <t>243120; 295973</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP19C02-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP19C02-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8,24%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6,43%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12,27%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>15,96%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>3,66%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>7,7%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>16,85%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8,24%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,43%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>12,28%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,9; 31,67</t>
+          <t>2,55; 21,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,76</t>
+          <t>1,99; 16,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,01; 17,27</t>
+          <t>0,0; 10,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,06; 38,11</t>
+          <t>5,08; 27,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,56; 21,16</t>
+          <t>6,18; 32,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,04; 17,47</t>
+          <t>0,0; 18,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,86</t>
+          <t>2,16; 17,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,73; 25,84</t>
+          <t>4,27; 24,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,44; 21,27</t>
+          <t>4,91; 20,3</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,29; 12,95</t>
+          <t>1,27; 12,42</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,83; 10,59</t>
+          <t>1,83; 10,3</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,26; 26,21</t>
+          <t>6,34; 22,0</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>6,39%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3,79%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>10,02%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9,23%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>3,77%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2,46%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6,32%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>6,39%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,79%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>10,02%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2,31; 13,38</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1,05; 10,11</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4,97; 18,58</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4,34; 18,08</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 9,11</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,64</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2,3; 14,71</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>3,03; 13,03</t>
-        </is>
-      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 10,31</t>
+          <t>1,19; 10,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,01; 17,8</t>
+          <t>0,0; 8,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,31; 17,73</t>
+          <t>2,47; 15,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 7,1</t>
+          <t>1,21; 6,72</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,71; 8,23</t>
+          <t>1,4; 7,86</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,18; 10,83</t>
+          <t>3,19; 11,18</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,11; 12,99</t>
+          <t>4,66; 13,29</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5,39%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6,22%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>6,33%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1,96%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>9,63%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,86%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,39%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,01; 16,67</t>
+          <t>0,0; 8,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,94</t>
+          <t>1,72; 14,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,54; 21,66</t>
+          <t>0,0; 11,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,84; 16,02</t>
+          <t>1,63; 17,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,64</t>
+          <t>2,0; 17,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,73; 14,52</t>
+          <t>0,0; 10,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,43</t>
+          <t>2,38; 23,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,61; 17,79</t>
+          <t>1,9; 16,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 9,27</t>
+          <t>1,11; 10,07</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 9,49</t>
+          <t>0,96; 9,45</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,33; 12,93</t>
+          <t>2,22; 12,91</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,65; 13,1</t>
+          <t>2,69; 13,13</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9,36%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6,18%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9,93%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>3,97%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2,55%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>12,52%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11,9%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,36%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,18%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>11,08%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,91</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,42</t>
+          <t>3,14; 22,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,03; 23,03</t>
+          <t>1,66; 14,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,65; 23,23</t>
+          <t>2,19; 25,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 13,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,13; 21,28</t>
+          <t>0,0; 9,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 13,8</t>
+          <t>5,78; 22,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,46; 27,01</t>
+          <t>4,71; 23,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,77</t>
+          <t>0,0; 6,88</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,37; 12,39</t>
+          <t>2,55; 11,96</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,61; 15,03</t>
+          <t>5,12; 15,66</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,75; 19,54</t>
+          <t>5,16; 20,03</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>12,48%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>4,7%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>74,38%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>74,04%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>23,34%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>6,38%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>71,64%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>71,77%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>12,48%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4,7%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>74,38%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>73,16%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,83; 36,87</t>
+          <t>3,2; 28,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,55</t>
+          <t>0,0; 14,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47,24; 87,81</t>
+          <t>54,46; 89,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57,85; 82,67</t>
+          <t>62,09; 84,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,23; 28,44</t>
+          <t>12,33; 40,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,56</t>
+          <t>0,0; 20,59</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,17; 89,06</t>
+          <t>50,02; 88,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>61,7; 84,7</t>
+          <t>57,96; 82,21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,83; 27,96</t>
+          <t>11,16; 28,71</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,41; 12,82</t>
+          <t>1,36; 12,8</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56,56; 83,12</t>
+          <t>58,41; 85,17</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>63,19; 80,69</t>
+          <t>63,46; 80,75</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4,19%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>8,59%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>20,02%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>5,41%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>6,36%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>26,07%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4,04%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>4,19%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>8,59%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>20,02%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,18</t>
+          <t>0,0; 14,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,01; 15,69</t>
+          <t>2,09; 19,8</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16,61; 39,43</t>
+          <t>9,84; 31,85</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,23</t>
+          <t>0,0; 16,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,11; 19,34</t>
+          <t>2,06; 15,46</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,78; 32,01</t>
+          <t>16,33; 39,09</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 15,64</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,18; 10,98</t>
+          <t>1,36; 12,64</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,22; 14,21</t>
+          <t>3,19; 14,27</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15,22; 31,65</t>
+          <t>15,51; 31,78</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,25</t>
+          <t>0,0; 8,11</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7,23%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3,85%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>24,88%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>21,83%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>7,52%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>4,78%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>13,96%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>15,73%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>7,23%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,85%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>24,88%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,85%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,22; 14,98</t>
+          <t>3,15; 13,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,15; 12,91</t>
+          <t>0,96; 9,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,98; 22,12</t>
+          <t>16,75; 34,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,24; 23,62</t>
+          <t>13,66; 34,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,13; 13,58</t>
+          <t>3,21; 14,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,95; 9,5</t>
+          <t>1,13; 10,35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,89; 34,95</t>
+          <t>8,22; 21,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,25; 32,43</t>
+          <t>10,34; 25,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,16; 11,92</t>
+          <t>4,14; 11,66</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,95; 7,87</t>
+          <t>2,05; 8,19</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14,21; 25,51</t>
+          <t>14,02; 25,86</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,35; 25,8</t>
+          <t>14,23; 26,94</t>
         </is>
       </c>
     </row>
@@ -1629,42 +1629,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>11,1%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>9,13%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>32,45%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>83,17%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>7,91%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>11,42%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>32,49%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>81,26%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>11,1%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>9,13%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>32,45%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>82,72%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,04; 13,07</t>
+          <t>6,47; 18,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,49; 18,2</t>
+          <t>4,35; 15,86</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24,63; 41,34</t>
+          <t>24,9; 41,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>73,1; 87,36</t>
+          <t>75,37; 89,58</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,31; 18,36</t>
+          <t>4,22; 13,67</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,33; 16,22</t>
+          <t>6,64; 18,38</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,77; 41,98</t>
+          <t>24,76; 41,32</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>75,32; 88,63</t>
+          <t>74,11; 88,38</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,17; 13,84</t>
+          <t>6,21; 13,46</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6,59; 14,91</t>
+          <t>6,8; 14,93</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26,9; 38,95</t>
+          <t>26,53; 38,5</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>76,33; 86,97</t>
+          <t>76,83; 86,81</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>6,67%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>6,34%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>19,55%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>33,71%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>7,34%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>5,76%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>18,97%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>29,71%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>6,67%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>6,34%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>19,55%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>32,62%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,27; 9,88</t>
+          <t>4,79; 9,18</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,92; 7,92</t>
+          <t>4,56; 8,85</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15,68; 22,44</t>
+          <t>15,92; 23,03</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>25,56; 33,51</t>
+          <t>29,28; 37,93</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,79; 9,03</t>
+          <t>5,47; 9,96</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,56; 8,66</t>
+          <t>4,02; 8,09</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,33; 23,38</t>
+          <t>15,77; 22,53</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>27,2; 35,82</t>
+          <t>26,78; 35,26</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,59; 8,53</t>
+          <t>5,61; 8,89</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4,8; 7,49</t>
+          <t>4,69; 7,74</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17,07; 21,7</t>
+          <t>16,83; 21,65</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>27,75; 33,78</t>
+          <t>29,68; 35,79</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2185</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1906</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4086</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>3084</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>818</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>2200</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5867</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2185</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1906</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>636</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5083</t>
+          <t>3629</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10950</t>
+          <t>7715</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1140; 6119</t>
+          <t>676; 5638</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4421</t>
+          <t>589; 4750</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>574; 4932</t>
+          <t>0; 3248</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2110; 13269</t>
+          <t>1693; 9172</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>678; 5610</t>
+          <t>1193; 6284</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>606; 5182</t>
+          <t>0; 4102</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3249</t>
+          <t>618; 4958</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1886; 10300</t>
+          <t>1259; 7122</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2494; 9749</t>
+          <t>2252; 9304</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1190; 6736</t>
+          <t>661; 6464</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1072; 6195</t>
+          <t>1070; 6022</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5418; 19572</t>
+          <t>3981; 13819</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,49 +2349,49 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4152</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2184</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5683</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6390</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>1314</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4353</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>4547</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>4152</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5683</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>6827</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>4152</t>
-        </is>
-      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>4183</t>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11180</t>
+          <t>10938</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>1501; 8695</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>605; 5827</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2817; 10541</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>3002; 12517</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0; 4832</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0; 4089</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1582; 10128</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>1967; 8463</t>
-        </is>
-      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>598; 5941</t>
+          <t>634; 5616</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2842; 10099</t>
+          <t>0; 4588</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3185; 13092</t>
+          <t>1677; 10733</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1517; 8676</t>
+          <t>1484; 8215</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1894; 9108</t>
+          <t>1555; 8699</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3504; 11944</t>
+          <t>3514; 12323</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5867; 18530</t>
+          <t>6400; 18233</t>
         </is>
       </c>
     </row>
@@ -2489,37 +2489,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -2557,42 +2557,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2127</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>718</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2204</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>2172</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>3130</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1864</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>636</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2127</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>718</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2517</t>
+          <t>1853</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4381</t>
+          <t>4057</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>690; 5715</t>
+          <t>0; 3169</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3326</t>
+          <t>677; 5628</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>825; 7045</t>
+          <t>0; 3623</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>587; 5098</t>
+          <t>578; 6099</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3406</t>
+          <t>685; 5956</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>681; 5728</t>
+          <t>0; 3606</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3671</t>
+          <t>772; 7662</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>645; 7125</t>
+          <t>599; 5150</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>693; 6451</t>
+          <t>775; 7012</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>735; 6918</t>
+          <t>702; 6890</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1505; 8361</t>
+          <t>1433; 8343</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1908; 9416</t>
+          <t>1802; 8798</t>
         </is>
       </c>
     </row>
@@ -2697,42 +2697,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3859</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3152</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5379</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>1664</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1068</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>5826</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5097</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>3859</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3152</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>5386</t>
+          <t>5647</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10483</t>
+          <t>11026</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5417</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3520</t>
+          <t>1294; 9178</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2806; 10718</t>
+          <t>848; 7298</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1993; 9954</t>
+          <t>1185; 13643</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 5604</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1290; 8775</t>
+          <t>0; 4032</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>827; 7040</t>
+          <t>2692; 10414</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1441; 15843</t>
+          <t>2137; 10764</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 5658</t>
+          <t>0; 5751</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1965; 10284</t>
+          <t>2118; 9933</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4498; 14658</t>
+          <t>4994; 15273</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4823; 19833</t>
+          <t>5136; 19932</t>
         </is>
       </c>
     </row>
@@ -2905,42 +2905,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>35</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2973,42 +2973,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>2804</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>12695</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>24831</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>6112</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>1662</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>10778</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>18153</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2804</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1300</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>12695</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>25641</t>
+          <t>19092</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>43793</t>
+          <t>43923</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2836; 9656</t>
+          <t>719; 6423</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 5097</t>
+          <t>0; 3963</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7107; 13210</t>
+          <t>9295; 15216</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14632; 20910</t>
+          <t>20826; 28290</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>727; 6389</t>
+          <t>3230; 10504</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 4576</t>
+          <t>0; 5366</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9246; 15200</t>
+          <t>7526; 13269</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>21363; 29328</t>
+          <t>15356; 21782</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4782; 13607</t>
+          <t>5433; 13970</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>760; 6885</t>
+          <t>728; 6872</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18162; 26691</t>
+          <t>18758; 27348</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>37862; 48350</t>
+          <t>38100; 48480</t>
         </is>
       </c>
     </row>
@@ -3118,37 +3118,37 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1187</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2849</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>8122</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>1372</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>2207</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>10360</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1091</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>1187</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>2849</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>8122</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>1215</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4606</t>
+          <t>0; 4049</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>696; 5441</t>
+          <t>693; 6566</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6603; 15671</t>
+          <t>3993; 12922</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 3424</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4034</t>
+          <t>0; 4192</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>699; 6414</t>
+          <t>715; 5360</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3968; 12986</t>
+          <t>6490; 15536</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4348</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>632; 5896</t>
+          <t>732; 6787</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2184; 9642</t>
+          <t>2161; 9683</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12227; 25417</t>
+          <t>12459; 25524</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 3369</t>
+          <t>0; 4227</t>
         </is>
       </c>
     </row>
@@ -3331,32 +3331,32 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>4918</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2588</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>15410</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>22404</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>4906</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>3057</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>9417</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>12233</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>4918</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>2588</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>15410</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>22850</t>
+          <t>13062</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>35083</t>
+          <t>35466</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2101; 9778</t>
+          <t>2145; 9176</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>733; 8257</t>
+          <t>645; 6367</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5383; 14919</t>
+          <t>10375; 21539</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7186; 18370</t>
+          <t>14017; 35914</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2127; 9238</t>
+          <t>2094; 9320</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>638; 6384</t>
+          <t>724; 6619</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9840; 21652</t>
+          <t>5541; 14702</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>14396; 35250</t>
+          <t>7864; 19489</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5545; 15888</t>
+          <t>5516; 15551</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2561; 10314</t>
+          <t>2684; 10737</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>18380; 33008</t>
+          <t>18138; 33453</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>24892; 48098</t>
+          <t>25429; 48148</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>90</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>8260</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>6400</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>25524</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>90153</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>6431</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>8893</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>25753</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>67682</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>8260</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>6400</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>25524</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>84206</t>
+          <t>75213</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>151888</t>
+          <t>165366</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>3286; 10630</t>
+          <t>4811; 13431</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>5053; 14167</t>
+          <t>3047; 11115</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>19518; 32760</t>
+          <t>19589; 32961</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>60887; 72768</t>
+          <t>81701; 97111</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4696; 13665</t>
+          <t>3431; 11117</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3032; 11369</t>
+          <t>5167; 14309</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>18696; 33018</t>
+          <t>19622; 32743</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>76656; 90207</t>
+          <t>67816; 80867</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>9611; 21551</t>
+          <t>9678; 20958</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>9748; 22052</t>
+          <t>10053; 22089</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>42474; 61511</t>
+          <t>41897; 60795</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>141267; 160955</t>
+          <t>153595; 173542</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>165</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>24141</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>23211</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>71938</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>155447</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>25741</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>20361</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>68778</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>116339</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>24141</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>23211</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>71938</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>152510</t>
+          <t>124258</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>268849</t>
+          <t>279704</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>18506; 34662</t>
+          <t>17335; 33220</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>13830; 27968</t>
+          <t>16688; 32387</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>56846; 81368</t>
+          <t>58586; 84759</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>100101; 131230</t>
+          <t>135027; 174902</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>17312; 32665</t>
+          <t>19209; 34955</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16690; 31697</t>
+          <t>14207; 28582</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>60081; 86057</t>
+          <t>57202; 81714</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>131763; 173549</t>
+          <t>106109; 139724</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>39819; 60805</t>
+          <t>39954; 63354</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>34508; 53864</t>
+          <t>33764; 55641</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>124700; 158533</t>
+          <t>122953; 158157</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>243120; 295973</t>
+          <t>254485; 306859</t>
         </is>
       </c>
     </row>
